--- a/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_pro_naive.xlsx
+++ b/Analysed/Gemini/Analysis_Summary_Depth_without_vernier_pro_naive.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8.6853 ± 2.6606</t>
+          <t>12.8707 ± 7.4005</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>9.7511 ± 3.1473</t>
+          <t>15.0331 ± 9.0973</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7089 ± 0.1808</t>
+          <t>0.5040 ± 0.3027</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -521,38 +521,114 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
-        <v>10.56666666666666</v>
+        <v>8.613412698412699</v>
       </c>
       <c r="D2" t="n">
-        <v>11.9765522028114</v>
+        <v>9.249851092752532</v>
       </c>
       <c r="E2" t="n">
-        <v>0.581081081081081</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="B3" t="n">
+        <v>82</v>
+      </c>
+      <c r="C3" t="n">
+        <v>26.51463414634146</v>
+      </c>
+      <c r="D3" t="n">
+        <v>30.78132752806877</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.4197530864197531</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>56</v>
+      </c>
+      <c r="C4" t="n">
+        <v>8.693571428571429</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.567626963583274</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.1454545454545454</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>45</v>
+      </c>
+      <c r="C5" t="n">
+        <v>16.03200000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>21.09738562002411</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8409090909090909</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" t="n">
+        <v>10.56666666666666</v>
+      </c>
+      <c r="D6" t="n">
+        <v>11.9765522028114</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.581081081081081</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>50</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C7" t="n">
         <v>6.803999999999998</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D7" t="n">
         <v>7.525629541772568</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E7" t="n">
         <v>0.8367346938775511</v>
       </c>
     </row>
